--- a/Docs/KNOWLEDGE_BASE/REGISTRY/IMPLEMENTATION_GAP_REGISTER.xlsx
+++ b/Docs/KNOWLEDGE_BASE/REGISTRY/IMPLEMENTATION_GAP_REGISTER.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R5cd0dfbef9664838"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="Rd20b9ee0fd4248f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R5e2b2f31533640c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="Rb5573a62110f4ff8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -570,8 +570,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A5)</x:f>
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -623,6 +622,40 @@
       </x:c>
       <x:c r="E5" t="str">
         <x:v>追加V72智能决策、Arena、模型和后续缺口记录；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>IMPLEMENTATION_GAP_REGISTER.xlsx</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LUOYANG-184-T4-LIVING-WORLD-COMPLETION-MASTER-V1</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>追加洛阳T4 Phase 0—19正式状态、完成证据与Deferred边界；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>IMPLEMENTATION_GAP_REGISTER.xlsx</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>HAN-WORLD-STYLE-D-STRATEGIC-LANDSCAPE-VISUAL-REFINEMENT-AND-ZHONGHUA-SOURCE-RECOVERY-V2</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>登记V2视觉仍为PARTIAL的锐弯接缝、汇流、城市块状感和连续过渡缺口。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -631,7 +664,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ce0eedae0f4165"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88c87aaa2edb48e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -679,8 +712,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A45)</x:f>
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2467,13 +2499,255 @@
       <x:c r="O45" s="56"/>
       <x:c r="P45" s="56"/>
     </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>IMP-GAP-LUOYANG-T4-001</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>LuoyangLogistics</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>城门状态应影响每条Shipment/Movement的真实路线与时长</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>城防设施与路线接口存在；逐路动态重算未纳入T4 V1</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>缺少城门关闭后的逐Shipment/Movement路径重算</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>S2</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>LUOYANG-GATE-ROUTE-RECALCULATION-V1</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1/LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>One Cell world|real route|determinism|save compatibility</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Does not block T4 V1</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>Post-T4 route deepening</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Deferred enhancement</x:v>
+      </x:c>
+      <x:c r="O46"/>
+      <x:c r="P46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>gap.map-presentation.dem-chunk-terrain.v1</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Formal DEM-derived 16x16 Cell visual chunks and unloading</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Continuous original Golden Slice background plus bound splines</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>Full DEM terrain mesh and chunk streaming remain deferred</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="H47" t="str"/>
+      <x:c r="I47" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J47" t="str"/>
+      <x:c r="K47" t="str"/>
+      <x:c r="L47" t="str">
+        <x:v>LUOYANG-FULL-CITY-MAP-PRESENTATION-AND-INTERACTION-V1</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="N47" t="str"/>
+      <x:c r="O47" t="str"/>
+      <x:c r="P47" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>gap.global-spatial.henan-high-detail-terrain.v1</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Final 河南尹 Terrain must use benchmarked Terrain and Streaming sizes over frozen Global Cells.</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Global Cell and Region membership contracts are frozen; the former direct-to-terrain step is superseded by a required block-size benchmark.</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>Historical entry preserved and rerouted through the benchmark gate.</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="H48"/>
+      <x:c r="I48" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_REGION_CELL_BOUNDARY_AND_TECHNICAL_BLOCK_SEMANTICS_CORRECTION_V1/WORLD_REGION_CELL_BOUNDARY_AND_TECHNICAL_BLOCK_SEMANTICS_CORRECTION_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48" t="str">
+        <x:v>MAP-TERRAIN-STREAMING-BLOCK-SIZE-BENCHMARK-V1</x:v>
+      </x:c>
+      <x:c r="M48" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>gap.global-spatial.vector-anchor-runtime-index.v1</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>River and road visual segments retain canonical global feature identity.</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Global GeoJSON/raster/route anchors are audited; runtime visual segment index is deferred.</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>No final Region terrain spline/mesh segment cache yet.</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H49" t="str"/>
+      <x:c r="I49" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J49" t="str"/>
+      <x:c r="K49" t="str"/>
+      <x:c r="L49" t="str">
+        <x:v>HENAN-YIN-REGION-TERRAIN-AND-LUOYANG-BUILDABLE-MAP-V1</x:v>
+      </x:c>
+      <x:c r="M49" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="N49" t="str"/>
+      <x:c r="O49" t="str"/>
+      <x:c r="P49" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>gap.global-spatial.terrain-streaming-block-benchmark.v1</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Benchmark 4x4, 8x8 and 16x16 candidates independently for Terrain Tile and Streaming Unit.</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>16x16 is retained only as a technical simulation aggregation block; Terrain and Streaming sizes are NOT_YET_FROZEN.</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>Real Unity DEM, memory, LOD and loading evidence is required before 河南尹 Terrain production.</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="H50" t="str"/>
+      <x:c r="I50" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_REGION_CELL_BOUNDARY_AND_TECHNICAL_BLOCK_SEMANTICS_CORRECTION_V1/validation_summary.json</x:v>
+      </x:c>
+      <x:c r="J50" t="str"/>
+      <x:c r="K50" t="str"/>
+      <x:c r="L50" t="str">
+        <x:v>MAP-TERRAIN-STREAMING-BLOCK-SIZE-BENCHMARK-V1</x:v>
+      </x:c>
+      <x:c r="M50" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="N50" t="str"/>
+      <x:c r="O50" t="str"/>
+      <x:c r="P50" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>IMP-GAP-STYLE-D-V2-001</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>Style D V2 river/terrain visual acceptance</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>Adaptive river ribbon, forest LOD and presentation terrain detail prototype implemented</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>One river source-segment endpoint seam, confluence union, low-frequency city terrain blocks and continuous LOD morph remain PARTIAL</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>S2</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>HAN-WORLD-STYLE-D-V3-USER-REVIEW-FOLLOWUP</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>08/13/14 V2 screenshots and VISUAL_ACCEPTANCE_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J51" t="str">
+        <x:v>Preserve canonical geometry and 2000m Cell facts</x:v>
+      </x:c>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
+      <x:c r="M51" t="str">
+        <x:v>User review follow-up</x:v>
+      </x:c>
+      <x:c r="N51" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="O51" t="str">
+        <x:v>No nationwide rollout before review</x:v>
+      </x:c>
+      <x:c r="P51"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56dc2de6a22b4fc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2d6a95247294db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>